--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_quarterly.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -916,50 +916,54 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10.17834612260288</v>
+        <v>1.443337143630821</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3108792038122499</v>
+        <v>-0.8493735639148458</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4325761954003344</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0830167089904766</v>
+        <v>0.1593744496576403</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.164563240394407</v>
+        <v>0.128109431975434</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9098267537631355</v>
+        <v>0.8687872763419483</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.09022589446255025</v>
+        <v>0.03248582446029458</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.3974800294591584</v>
+        <v>0.08583583756568453</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5599655894391498</v>
+        <v>0.1160814188458357</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.2455127207029907</v>
+        <v>0.07509850242737019</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.6051970115039702</v>
+        <v>1.139014180044933</v>
       </c>
       <c r="V4" s="2" t="n">
         <v>0.3333333333333333</v>
@@ -970,23 +974,23 @@
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>-0.1667370828161092</v>
+        <v>-0.8178673111714756</v>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
@@ -998,19 +1002,19 @@
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1028,7 +1032,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1059,44 +1063,44 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.443337143630821</v>
+        <v>10.15900048247641</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.8493735639148458</v>
+        <v>-0.3120718205715182</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.4325761954003344</v>
+        <v>-0.4324636107084076</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1593744496576403</v>
+        <v>0.1325483513612503</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.128109431975434</v>
+        <v>0.178764949937706</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8687872763419483</v>
+        <v>0.9180630502698097</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.03248582446029458</v>
+        <v>0.09015831897637328</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.08583583756568453</v>
+        <v>0.3655489061444048</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.1160814188458357</v>
+        <v>0.5104256463073169</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.07509850242737019</v>
+        <v>0.2084760815567517</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.139014180044933</v>
+        <v>1.304320163452614</v>
       </c>
       <c r="V5" s="2" t="n">
         <v>0.3333333333333333</v>
@@ -1115,15 +1119,15 @@
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>-0.8178673111714756</v>
+        <v>-0.1681791570147225</v>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
@@ -1135,19 +1139,19 @@
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1165,7 +1169,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1183,68 +1187,64 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.15900048247641</v>
+        <v>4.497265701071065</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3120718205715182</v>
+        <v>-0.6611054913465499</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4324636107084076</v>
+        <v>-0.6167887185672993</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1325483513612503</v>
+        <v>0.2554437570764661</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.178764949937706</v>
+        <v>0.1602520209182536</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9180630502698097</v>
+        <v>0.9544163589889236</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.09015831897637328</v>
+        <v>0.06288521031877381</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.3655489061444048</v>
+        <v>0.2496931566495985</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5104256463073169</v>
+        <v>0.3450845275415115</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.2084760815567517</v>
+        <v>0.1019558374297863</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.304320163452614</v>
+        <v>1.870237883382897</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
@@ -1256,67 +1256,47 @@
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1681791570147225</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.001730635275942749</v>
-      </c>
+        <v>-0.5902195544520488</v>
+      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AJ6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
           <t>0/6</t>
         </is>
       </c>
-      <c r="AL6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1326,7 +1306,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1357,51 +1337,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.497265701071065</v>
+        <v>10.61412189973661</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.6611054913465499</v>
+        <v>-0.2840145722107547</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.6167887185672993</v>
+        <v>-0.5687350964668526</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2554437570764661</v>
+        <v>0.1968947767064457</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1602520209182536</v>
+        <v>0.1872340047983837</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9544163589889236</v>
+        <v>0.9297074694689009</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.06288521031877381</v>
+        <v>0.09171893939237674</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2496931566495985</v>
+        <v>0.3566613011072807</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.3450845275415115</v>
+        <v>0.4996826264223795</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0.1019558374297863</v>
+        <v>0.1612682951380377</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.870237883382897</v>
+        <v>1.798433611188803</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
@@ -1413,23 +1393,23 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>-0.5902195544520488</v>
+        <v>-0.1342532259637707</v>
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
@@ -1441,11 +1421,11 @@
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1463,7 +1443,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1481,140 +1461,116 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.61412189973661</v>
+        <v>2.447060668526191</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.2840145722107547</v>
+        <v>-0.7874961853615314</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5687350964668526</v>
+        <v>-0.386058675102369</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1968947767064457</v>
+        <v>0.1631469974330323</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1872340047983837</v>
+        <v>0.1238873680000992</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9297074694689009</v>
+        <v>0.878869639307015</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.09171893939237674</v>
+        <v>0.04528029830649594</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.3566613011072807</v>
+        <v>0.1881759445545135</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.4996826264223795</v>
+        <v>0.2563416833653955</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.1612682951380377</v>
+        <v>0.1172886434801373</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.798433611188803</v>
+        <v>1.92758584033941</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>-0.7430471559153002</v>
+      </c>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.1342532259637707</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.03898392234004788</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
       <c r="AH8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AJ8" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AN8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1624,7 +1580,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1655,51 +1611,51 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.447060668526191</v>
+        <v>10.98508615081609</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.7874961853615314</v>
+        <v>-0.2611454306349558</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.386058675102369</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1631469974330323</v>
+        <v>0.145373924020359</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1238873680000992</v>
+        <v>0.1780193492151014</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.878869639307015</v>
+        <v>0.9234592445328031</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.04528029830649594</v>
+        <v>0.09294796267145866</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1881759445545135</v>
+        <v>0.3814407560037183</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.2563416833653955</v>
+        <v>0.5340195317796141</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>0.1172886434801373</v>
+        <v>0.1874615928218248</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1.92758584033941</v>
+        <v>1.836146217807533</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
@@ -1711,23 +1667,23 @@
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>-0.7430471559153002</v>
+        <v>-0.1066005883879488</v>
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
@@ -1739,11 +1695,11 @@
         </is>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1752,167 +1708,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>10.98508615081609</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.2611454306349558</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.145373924020359</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1780193492151014</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9234592445328031</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0.09294796267145866</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.3814407560037183</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5340195317796141</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>0.1874615928218248</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1.836146217807533</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.1066005883879488</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.072169891624841</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1925,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2310,7 +2105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2320,7 +2115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2331,68 +2126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4836144302039722</v>
+        <v>0.09180870584028344</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.6365165293445558</v>
+        <v>0.2043310968229539</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.2212307393619097</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.08703159251923893</v>
+        <v>0.1451694086489946</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1493056045470308</v>
+        <v>0.1041195199922966</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9412742382271468</v>
+        <v>0.9756232686980609</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.154578844788938</v>
+        <v>-0.1676178254853798</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.5965164192632566</v>
+        <v>0.5718932516928532</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.3285703899194556</v>
+        <v>0.3562858446275809</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.2212307393619097</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7548820739334152</v>
+        <v>0.3116675720223592</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.02505461866766034</v>
+        <v>-0.2338340434212389</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.060244241089977</v>
+        <v>0.4377422113753213</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.07218203518241495</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.7263503729691916</v>
+        <v>0.2704408424224136</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.7205378142852468</v>
+        <v>0.6940018573723128</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.003378338235686673</v>
+        <v>-0.2500357441206794</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2408,7 +2207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2439,62 +2238,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.09180870584028344</v>
+        <v>0.1072953106862609</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2043310968229539</v>
+        <v>0.2214137594729695</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2212307393619097</v>
+        <v>-0.4324281870017384</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1451694086489946</v>
+        <v>0.2036681684298383</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1041195199922966</v>
+        <v>0.1621472165416299</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9756232686980609</v>
+        <v>0.9789473684210527</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1676178254853798</v>
+        <v>-0.3804356199995604</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.5718932516928532</v>
+        <v>0.1700023111137057</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.3562858446275809</v>
+        <v>0.8086480408957659</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2212307393619097</v>
+        <v>-0.4324281870017384</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3116675720223592</v>
+        <v>0.7872158994767828</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2338340434212389</v>
+        <v>0.04394132205630119</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.4377422113753213</v>
+        <v>1.105657628834282</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07218203518241495</v>
+        <v>-0.1156623821440808</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.2704408424224136</v>
+        <v>0.288461229328602</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.6940018573723128</v>
+        <v>0.2608910217166545</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2500357441206794</v>
+        <v>0.02186565463398371</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2510,7 +2309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2528,89 +2327,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1072953106862609</v>
+        <v>-0.3166303960343169</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2214137594729695</v>
+        <v>-0.2462019580196928</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4324281870017384</v>
+        <v>-0.6167647998119878</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2036681684298383</v>
+        <v>0.441784976019348</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1621472165416299</v>
+        <v>0.1668707085500485</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9789473684210527</v>
+        <v>0.9988919667590028</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3804356199995604</v>
+        <v>-0.5651990807842828</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1700023111137057</v>
+        <v>-0.1789100587796997</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8086480408957659</v>
+        <v>1.201378381427129</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4324281870017384</v>
+        <v>-0.6167647998119878</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7872158994767828</v>
+        <v>0.5716838989170674</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.04394132205630119</v>
+        <v>-0.08195435830085074</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.105657628834282</v>
+        <v>0.802939402696889</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.1220228475473601</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.288461229328602</v>
+        <v>-0.2048234725515767</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2608910217166545</v>
+        <v>-0.1151257351611188</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.02186565463398371</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.2536502152152657</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.2671529731879451</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.01842507027887863</v>
-      </c>
+        <v>-0.1013677772703563</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -2622,7 +2411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2653,23 +2442,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.3166303960343169</v>
+        <v>-0.1509545937884657</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2462019580196928</v>
+        <v>-0.06345151870880028</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.6167647998119878</v>
+        <v>-0.5687081783665724</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.441784976019348</v>
+        <v>0.3453849329396694</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1668707085500485</v>
+        <v>0.1761679438089752</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.9988919667590028</v>
@@ -2678,37 +2467,37 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.5651990807842828</v>
+        <v>-0.5252150592986788</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1789100587796997</v>
+        <v>-0.1034031396347619</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.201378381427129</v>
+        <v>1.116388966814729</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.6167647998119878</v>
+        <v>-0.5687081783665724</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5716838989170674</v>
+        <v>0.7882736654565754</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.08195435830085074</v>
+        <v>0.04455918004183834</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.802939402696889</v>
+        <v>1.107143278483707</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1220228475473601</v>
+        <v>-0.1229482572702627</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2048234725515767</v>
+        <v>-0.01204125287488278</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.1151257351611188</v>
+        <v>-0.03375324937798174</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1013677772703563</v>
+        <v>0.02247044710796886</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2724,7 +2513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2742,89 +2531,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.1509545937884657</v>
+        <v>-0.03531692510718976</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.06345151870880028</v>
+        <v>0.06410383014673715</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5687081783665724</v>
+        <v>-0.3860586751023685</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.3453849329396694</v>
+        <v>0.2627667438659022</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1761679438089752</v>
+        <v>0.1170982492244087</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9955678670360111</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.5252150592986788</v>
+        <v>-0.3482013611471607</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1034031396347619</v>
+        <v>0.2308743666607311</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.116388966814729</v>
+        <v>0.740131401284706</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.5687081783665724</v>
+        <v>-0.3814494404070007</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7882736654565754</v>
+        <v>0.4800323556837203</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.04455918004183834</v>
+        <v>-0.1354894870111152</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.107143278483707</v>
+        <v>0.6742133085748864</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1229482572702627</v>
+        <v>-0.07218203518241484</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01204125287488278</v>
+        <v>0.1225160339734006</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.03375324937798174</v>
+        <v>0.3264917710345101</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.02247044710796886</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.4277182879012542</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.4384042346529764</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.0190278264386825</v>
-      </c>
+        <v>-0.1537708273169551</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -2836,7 +2615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2867,180 +2646,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.03531692510718976</v>
+        <v>0.03485048027329096</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.06410383014673715</v>
+        <v>0.1415027259707617</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3860586751023685</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2627667438659022</v>
+        <v>0.252789065656861</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1170982492244087</v>
+        <v>0.1629974290144591</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9955678670360111</v>
+        <v>0.9933518005540166</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3482013611471607</v>
+        <v>-0.4284675262734969</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2308743666607311</v>
+        <v>0.07929754634388031</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.740131401284706</v>
+        <v>0.9107439143288391</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3814494404070007</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4800323556837203</v>
+        <v>0.8106591101042158</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1354894870111152</v>
+        <v>0.0576348754220759</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6742133085748864</v>
+        <v>1.13858400226223</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07218203518241484</v>
+        <v>-0.1156623821440808</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1225160339734006</v>
+        <v>0.2041636130092959</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3264917710345101</v>
+        <v>0.1631400835870296</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1537708273169551</v>
+        <v>0.03526963776861081</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.03485048027329096</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.1415027259707617</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.252789065656861</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1629974290144591</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9933518005540166</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.4284675262734969</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.07929754634388031</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.9107439143288391</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.8106591101042158</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.0576348754220759</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.13858400226223</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1156623821440808</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.2041636130092959</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.1631400835870296</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0.03526963776861081</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.302480173281264</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.3239671491496824</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.03178392269161501</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3053,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3438,7 +3105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3448,7 +3115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3459,74 +3126,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4350331494949515</v>
+        <v>0.05330476645442528</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.3622676312689921</v>
+        <v>-0.0001046389017532734</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.1365494988551755</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1166796953447241</v>
+        <v>0.04436078156857341</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1997642353548091</v>
+        <v>0.07838093185860415</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9244186046511628</v>
+        <v>0.3561046511627907</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2739414126958895</v>
+        <v>1.058870045499049</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7298771057515232</v>
+        <v>-0.04411026616389809</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.268826669726443</v>
+        <v>0.03041923040339545</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.06933303030489379</v>
+        <v>-0.5143475114982876</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.13114252804588</v>
+        <v>0.02711834957498587</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1170212548420333</v>
+        <v>-0.1365494988551758</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.120434289343607</v>
+        <v>-0.1776086999244962</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1332626360681237</v>
+        <v>0.8315131856388851</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.01131983559347249</v>
+        <v>-0.5509771338126459</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1475930532307546</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1079725986742808</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3536,7 +3211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3567,62 +3242,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.05330476645442528</v>
+        <v>0.3169134849931055</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.0001046389017532734</v>
+        <v>0.2501374023444205</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1365494988551755</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04436078156857341</v>
+        <v>0.1173744075779711</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.07838093185860415</v>
+        <v>0.2016898091529489</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3561046511627907</v>
+        <v>0.9375</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499049</v>
+        <v>0.2739414126958895</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389809</v>
+        <v>0.7298771057515232</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.03041923040339545</v>
+        <v>1.082076248570495</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.5143475114982876</v>
+        <v>-0.01868532580402937</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.02711834957498587</v>
+        <v>0.9646569484627249</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1365494988551758</v>
+        <v>-0.1198660820476311</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1776086999244962</v>
+        <v>0.02820971432231989</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.8315131856388851</v>
+        <v>0.1332626360681237</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5509771338126459</v>
+        <v>-0.09269953707314182</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3631,7 +3306,7 @@
         <v>0.1475930532307546</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1079725986742808</v>
+        <v>-0.007539848144645811</v>
       </c>
     </row>
     <row r="6">
@@ -3642,7 +3317,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3660,95 +3335,81 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3169134849931055</v>
+        <v>0.3454968097333002</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2501374023444205</v>
+        <v>0.2772713665328586</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2347571285205642</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1173744075779711</v>
+        <v>0.0619851418071798</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2016898091529489</v>
+        <v>0.1352481678306468</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9375</v>
+        <v>0.9418604651162791</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2253489755584758</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2739414126958895</v>
+        <v>0.5602526913132901</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7298771057515232</v>
+        <v>0.4475567713595454</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2347571285205642</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.082076248570495</v>
+        <v>0.7369070294631324</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01868532580402937</v>
+        <v>-0.1813689066879554</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9646569484627249</v>
+        <v>0.6569430641156202</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1198660820476311</v>
+        <v>-0.1365494988551768</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.02820971432231989</v>
+        <v>0.05052678564128477</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1332626360681237</v>
+        <v>0.3879571385848151</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.09269953707314182</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.08231145360190273</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.08231145360190262</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1475930532307546</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.007539848144645811</v>
-      </c>
+        <v>-0.2431129489254835</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3758,7 +3419,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3789,62 +3450,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3454968097333002</v>
+        <v>0.4287589137569821</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2772713665328586</v>
+        <v>0.3563115401084533</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2347571285205642</v>
+        <v>-0.3717086876431007</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.0619851418071798</v>
+        <v>0.1130847159364414</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1352481678306468</v>
+        <v>0.207610581704922</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9418604651162791</v>
+        <v>0.9236918604651163</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2253489755584758</v>
+        <v>-0.3639842631607436</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.5602526913132901</v>
+        <v>0.2810223362661595</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.4475567713595454</v>
+        <v>0.722894884443944</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2347571285205642</v>
+        <v>-0.3717086876431007</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7369070294631324</v>
+        <v>1.246420695276098</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1813689066879554</v>
+        <v>0.05877274869518856</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6569430641156202</v>
+        <v>1.111167892275843</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1365494988551768</v>
+        <v>-0.1198660820476312</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.05052678564128477</v>
+        <v>0.1155355391908874</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3879571385848151</v>
+        <v>0.1395616275531872</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2431129489254835</v>
+        <v>-0.02108362354556237</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3860,7 +3521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3878,89 +3539,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4287589137569821</v>
+        <v>0.2397270581692568</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.3563115401084533</v>
+        <v>0.1768648296011024</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3717086876431007</v>
+        <v>-0.1198660820476312</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1130847159364414</v>
+        <v>0.04797087557380604</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.207610581704922</v>
+        <v>0.1081360511451568</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9236918604651163</v>
+        <v>0.9106104651162791</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3639842631607436</v>
+        <v>-0.008209339511976887</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.2810223362661595</v>
+        <v>0.9976014985088748</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.722894884443944</v>
+        <v>0.01630424756921656</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3717086876431007</v>
+        <v>-0.06689328315495324</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.246420695276098</v>
+        <v>0.2499886392953465</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.05877274869518856</v>
+        <v>-0.4108610598862772</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.111167892275843</v>
+        <v>0.2228616312866858</v>
       </c>
       <c r="X8" s="2" t="n">
         <v>-0.1198660820476312</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1155355391908874</v>
+        <v>-0.03205531810274154</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1395616275531872</v>
+        <v>0.7770104005200507</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02108362354556237</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.004372188712280067</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.005558280388487713</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.00987557786996851</v>
-      </c>
+        <v>-0.455295995108422</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -3972,7 +3623,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4003,180 +3654,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2397270581692568</v>
+        <v>0.476378731544906</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.1768648296011024</v>
+        <v>0.4015167232794812</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1198660820476312</v>
+        <v>-0.3639469600214459</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04797087557380604</v>
+        <v>0.1121637776951362</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1081360511451568</v>
+        <v>0.2042768068824445</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9106104651162791</v>
+        <v>0.9236918604651163</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.008209339511976887</v>
+        <v>-0.3561271102519857</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.9976014985088748</v>
+        <v>0.2968477125777542</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.01630424756921656</v>
+        <v>0.7072901008889843</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.06689328315495324</v>
+        <v>-0.3639469600214459</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.2499886392953465</v>
+        <v>1.292966135167922</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.4108610598862772</v>
+        <v>0.08071033297631836</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2228616312866858</v>
+        <v>1.152662548562976</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1198660820476312</v>
+        <v>-0.1198660820476313</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.03205531810274154</v>
+        <v>0.1527157790485258</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.7770104005200507</v>
+        <v>0.1536394395286185</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.455295995108422</v>
+        <v>-0.000800649187643665</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.476378731544906</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.4015167232794812</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3639469600214459</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1121637776951362</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2042768068824445</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9236918604651163</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.3561271102519857</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.2968477125777542</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7072901008889843</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3639469600214459</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1.292966135167922</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.08071033297631836</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.152662548562976</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1198660820476313</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.1527157790485258</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.1536394395286185</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.000800649187643665</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.0288115867319898</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.01798065409726401</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.01063962521402773</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4189,7 +3728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4574,7 +4113,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4584,7 +4123,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4595,74 +4134,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.004463254504794456</v>
+        <v>0.0008500212579751754</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.01851322395813138</v>
+        <v>-0.02204380671922623</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1971519721341342</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04623052871931452</v>
+        <v>0.07990143847314349</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1529248250153883</v>
+        <v>0.2116131333080739</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9586206896551724</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1350492147242663</v>
+        <v>-0.1968052513911284</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07505645280409468</v>
+        <v>-0.001700776449303554</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.691011962901241</v>
+        <v>1.00700165751219</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1971519721341342</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1612952685910172</v>
+        <v>0.2460863607380914</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08703698909779678</v>
+        <v>-0.02037768816204011</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5929822223968276</v>
+        <v>0.9047062469143481</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02174145290462626</v>
+        <v>-0.03283822635553379</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.001115049111132582</v>
+        <v>-0.004708216206208204</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.07181777702352021</v>
+        <v>-0.004708216206208093</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.06804591946327887</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.2004725031597112</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1592411666562514</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4672,7 +4219,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4703,62 +4250,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0008500212579751754</v>
+        <v>-0.006391146990712304</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.02204380671922623</v>
+        <v>-0.02911933770287078</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1971519721341342</v>
+        <v>-0.2026163801193157</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.07990143847314349</v>
+        <v>0.0852684684349431</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2116131333080739</v>
+        <v>0.2120594124587969</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1968052513911284</v>
+        <v>-0.2026163801193158</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.001700776449303554</v>
+        <v>-0.008923489629824699</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.00700165751219</v>
+        <v>1.036735702818083</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1971519721341342</v>
+        <v>-0.2026163801193157</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2460863607380914</v>
+        <v>0.2460863607380916</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.02037768816204011</v>
+        <v>-0.02037768816203989</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9047062469143481</v>
+        <v>0.9047062469143489</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.03283822635553379</v>
+        <v>-0.03283822635553391</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.004708216206208204</v>
+        <v>-0.01190917050496365</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-0.004708216206208093</v>
+        <v>-0.01190917050496387</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -4767,7 +4314,7 @@
         <v>0.2004725031597112</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1592411666562514</v>
+        <v>-0.01980775507866428</v>
       </c>
     </row>
     <row r="6">
@@ -4778,7 +4325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4796,95 +4343,81 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.006391146990712304</v>
+        <v>-0.1018000785001284</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.02911933770287078</v>
+        <v>-0.1223458486506929</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0852684684349431</v>
+        <v>0.1102282466387932</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2120594124587969</v>
+        <v>0.1849974711385499</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9862068965517241</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2026163801193158</v>
+        <v>-0.1930057479754295</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.008923489629824699</v>
+        <v>0.003021666415692792</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.036735702818083</v>
+        <v>0.9875605795415207</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2460863607380916</v>
+        <v>0.1130189827826977</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.02037768816203989</v>
+        <v>-0.1249898374721931</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9047062469143489</v>
+        <v>0.4155003935883911</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.03283822635553391</v>
+        <v>-0.006326442692099143</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.01190917050496365</v>
+        <v>-0.106788246904953</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.01190917050496387</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.01080617080498181</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.07811677443995857</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.07301424059873263</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.2004725031597112</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.01980775507866428</v>
-      </c>
+        <v>-0.1067882469049533</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4894,7 +4427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4925,23 +4458,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1018000785001284</v>
+        <v>-0.03281284150392505</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1223458486506929</v>
+        <v>-0.05493665222287392</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-0.1964175293895148</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1102282466387932</v>
+        <v>0.08741987364983472</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1849974711385499</v>
+        <v>0.198908108056075</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.9862068965517241</v>
@@ -4962,25 +4495,25 @@
         <v>-0.1964175293895148</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1130189827826977</v>
+        <v>0.1985056350396743</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1249898374721931</v>
+        <v>-0.05778371552598793</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4155003935883911</v>
+        <v>0.7297815593251392</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.006326442692099143</v>
+        <v>-0.02015312857781415</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.106788246904953</v>
+        <v>-0.03818413169231205</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1067882469049533</v>
+        <v>-0.03818413169231216</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4996,7 +4529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5014,40 +4547,36 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.03281284150392505</v>
+        <v>-0.1018000785001288</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.05493665222287392</v>
+        <v>-0.1223458486506933</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.196417529389515</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.08741987364983472</v>
+        <v>0.1102282466387935</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.198908108056075</v>
+        <v>0.1849974711385499</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>0.9862068965517241</v>
@@ -5056,47 +4585,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.1930057479754297</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.003021666415692792</v>
+        <v>0.00302166641569257</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9875605795415207</v>
+        <v>0.9875605795415218</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.196417529389515</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1985056350396743</v>
+        <v>0.1130189827826975</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.05778371552598793</v>
+        <v>-0.1249898374721933</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7297815593251392</v>
+        <v>0.4155003935883903</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02015312857781415</v>
+        <v>-0.006326442692098921</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03818413169231205</v>
+        <v>-0.1067882469049535</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03818413169231216</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.03711046256948125</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.0670055848699963</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.03204212352798441</v>
-      </c>
+        <v>-0.1067882469049534</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -5108,7 +4631,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5139,23 +4662,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.1018000785001288</v>
+        <v>-0.03281284150392505</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1223458486506933</v>
+        <v>-0.05493665222287392</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.196417529389515</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1102282466387935</v>
+        <v>0.08741987364983472</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1849974711385499</v>
+        <v>0.198908108056075</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0.9862068965517241</v>
@@ -5164,155 +4687,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1930057479754297</v>
+        <v>-0.1930057479754295</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.00302166641569257</v>
+        <v>0.003021666415692792</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9875605795415218</v>
+        <v>0.9875605795415207</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.196417529389515</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1130189827826975</v>
+        <v>0.1985056350396743</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1249898374721933</v>
+        <v>-0.05778371552598793</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.4155003935883903</v>
+        <v>0.7297815593251392</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.006326442692098921</v>
+        <v>-0.02015312857781415</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1067882469049535</v>
+        <v>-0.03818413169231205</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1067882469049534</v>
+        <v>-0.03818413169231216</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.03281284150392505</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.05493665222287392</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1964175293895148</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.08741987364983472</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.198908108056075</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9862068965517241</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1930057479754295</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.003021666415692792</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.9875605795415207</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1964175293895148</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.1985056350396743</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.05778371552598793</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.7297815593251392</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.02015312857781415</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.03818413169231205</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.03818413169231216</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.03711046256948125</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.0670055848699963</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.03204212352798441</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5325,7 +4736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5710,7 +5121,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5720,7 +5131,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5731,68 +5142,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.005869330943017559</v>
+        <v>-0.2393739026337791</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08376291105473144</v>
+        <v>-0.307152708818292</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1140968231800305</v>
+        <v>0.2264340196757501</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4114240812492495</v>
+        <v>0.4091073817733869</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.007998698566999085</v>
+        <v>-0.02087617766040484</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.980437851023039</v>
+        <v>1.051056167955527</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4059102655834499</v>
+        <v>0.09448449043690843</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09103346041238103</v>
+        <v>-0.2923803145488134</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7424559969061268</v>
+        <v>0.172822868716239</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08544765322886072</v>
+        <v>-0.06547477152419368</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.02958110988967866</v>
+        <v>-0.2661810928233896</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02949052568081556</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.05737948441189333</v>
+        <v>-0.26618109282339</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5808,7 +5223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5839,23 +5254,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.2393739026337791</v>
+        <v>-0.03040624665895153</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.307152708818292</v>
+        <v>-0.1168059998530311</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2264340196757501</v>
+        <v>0.1399077070334797</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4091073817733869</v>
+        <v>0.4555303123429243</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -5864,37 +5279,37 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02087617766040484</v>
+        <v>-0.02087617766040506</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.051056167955527</v>
+        <v>1.051056167955528</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.09448449043690843</v>
+        <v>0.3951734350568115</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2923803145488134</v>
+        <v>-0.09797516923181782</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.172822868716239</v>
+        <v>0.7228171139111152</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06547477152419368</v>
+        <v>-0.0854476532288605</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2661810928233896</v>
+        <v>-0.06457820610456255</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.26618109282339</v>
+        <v>-0.06457820610456266</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5910,7 +5325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5928,40 +5343,36 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.03040624665895153</v>
+        <v>-0.2393739026337792</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1168059998530311</v>
+        <v>-0.3071527088182922</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>-0.3050371165491933</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1399077070334797</v>
+        <v>0.2264340196757502</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4555303123429243</v>
+        <v>0.409107381773387</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
@@ -5982,35 +5393,29 @@
         <v>-0.3050371165491933</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3951734350568115</v>
+        <v>0.09448449043690843</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.09797516923181782</v>
+        <v>-0.2923803145488134</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7228171139111152</v>
+        <v>0.172822868716239</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0854476532288605</v>
+        <v>-0.06547477152419368</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.06457820610456255</v>
+        <v>-0.2661810928233898</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.06457820610456266</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.03606390659904124</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.02864574752770366</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.007636924481935314</v>
-      </c>
+        <v>-0.26618109282339</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -6022,7 +5427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6053,23 +5458,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.2393739026337792</v>
+        <v>-0.03040624665895153</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3071527088182922</v>
+        <v>-0.1168059998530311</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-0.3050371165491933</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2264340196757502</v>
+        <v>0.1399077070334797</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.409107381773387</v>
+        <v>0.4555303123429243</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
@@ -6090,25 +5495,25 @@
         <v>-0.3050371165491933</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.09448449043690843</v>
+        <v>0.3951734350568115</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2923803145488134</v>
+        <v>-0.09797516923181782</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.172822868716239</v>
+        <v>0.7228171139111152</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.06547477152419368</v>
+        <v>-0.0854476532288605</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2661810928233898</v>
+        <v>-0.06457820610456255</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.26618109282339</v>
+        <v>-0.06457820610456266</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6124,7 +5529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6142,40 +5547,36 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.03040624665895153</v>
+        <v>-0.2393739026337796</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1168059998530311</v>
+        <v>-0.3071527088182925</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1399077070334797</v>
+        <v>0.2264340196757505</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4555303123429243</v>
+        <v>0.4091073817733872</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
@@ -6184,47 +5585,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02087617766040506</v>
+        <v>-0.02087617766040561</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.051056167955528</v>
+        <v>1.051056167955529</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.3951734350568115</v>
+        <v>0.09448449043690865</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.09797516923181782</v>
+        <v>-0.2923803145488132</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7228171139111152</v>
+        <v>0.1728228687162394</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0854476532288605</v>
+        <v>-0.0654747715241939</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.06457820610456255</v>
+        <v>-0.2661810928233901</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>-6.661338147750939e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.06457820610456266</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.03606390659904124</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.02864574752770366</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.007636924481935314</v>
-      </c>
+        <v>-0.2661810928233898</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -6236,7 +5631,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6267,23 +5662,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.2393739026337796</v>
+        <v>-0.03040624665895153</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.3071527088182925</v>
+        <v>-0.1168059998530311</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2264340196757505</v>
+        <v>0.1399077070334797</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4091073817733872</v>
+        <v>0.4555303123429243</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
@@ -6292,155 +5687,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.02087617766040561</v>
+        <v>-0.02087617766040506</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.051056167955529</v>
+        <v>1.051056167955528</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.09448449043690865</v>
+        <v>0.3951734350568115</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2923803145488132</v>
+        <v>-0.09797516923181782</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1728228687162394</v>
+        <v>0.7228171139111152</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0654747715241939</v>
+        <v>-0.0854476532288605</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.2661810928233901</v>
+        <v>-0.06457820610456255</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-6.661338147750939e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2661810928233898</v>
+        <v>-0.06457820610456266</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.03040624665895153</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.1168059998530311</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1399077070334797</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.4555303123429243</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>-0.02087617766040506</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>1.051056167955528</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.3951734350568115</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.09797516923181782</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.7228171139111152</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.0854476532288605</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.06457820610456255</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.06457820610456266</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.03606390659904124</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.02864574752770366</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.007636924481935314</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6453,7 +5736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6838,7 +6121,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6848,7 +6131,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6859,74 +6142,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.008347989224310126</v>
+        <v>-0.1528517297824459</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.06537597639031245</v>
+        <v>-0.2015695866079242</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2645312178855237</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1202141404246801</v>
+        <v>0.2010923836949493</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1643665908468291</v>
+        <v>0.1705899623566641</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.8791423001949318</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2214796402899178</v>
+        <v>-0.2519196755963159</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.128014615636332</v>
+        <v>0.08390940464494601</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7148394203240476</v>
+        <v>0.8130865421117908</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2618497648763229</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2737650318419123</v>
+        <v>0.1324295568030611</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1714433388946379</v>
+        <v>-0.2633790149153505</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5094914103593154</v>
+        <v>0.2464585093826474</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.09105587445754815</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.0398202447626419</v>
+        <v>-0.1797378415932688</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1064472207641982</v>
+        <v>0.06318529184396993</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.132195610221531</v>
+        <v>-0.2284861682161884</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.8811234607151575</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.4676866206072701</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6936,7 +6227,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6967,62 +6258,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.1528517297824459</v>
+        <v>-0.1253098049081549</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2015695866079242</v>
+        <v>-0.1756115445082261</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2645312178855237</v>
+        <v>-0.3130106839482674</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2010923836949493</v>
+        <v>0.2047087134872211</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1705899623566641</v>
+        <v>0.190171927237105</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8791423001949318</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2519196755963159</v>
+        <v>-0.2826185422289195</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.08390940464494601</v>
+        <v>0.03942916747048986</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8130865421117908</v>
+        <v>0.9121690582271763</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2618497648763229</v>
+        <v>-0.2826185422289196</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1324295568030611</v>
+        <v>0.2192818557222349</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2633790149153505</v>
+        <v>-0.2068834690314009</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2464585093826474</v>
+        <v>0.4080952968553129</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.09105587445754815</v>
+        <v>-0.1285213228736198</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1797378415932688</v>
+        <v>-0.1530700202232739</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.06318529184396993</v>
+        <v>0.01955550715997778</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2284861682161884</v>
+        <v>-0.169314496533993</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -7031,7 +6322,7 @@
         <v>0.8811234607151575</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.4676866206072701</v>
+        <v>-0.1500721998113352</v>
       </c>
     </row>
     <row r="6">
@@ -7042,7 +6333,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7060,95 +6351,81 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.1253098049081549</v>
+        <v>0.2380398983964456</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1756115445082261</v>
+        <v>0.1668426208539695</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3130106839482674</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2047087134872211</v>
+        <v>0.05142325442912488</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.190171927237105</v>
+        <v>0.1154607916375272</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9239766081871345</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2826185422289195</v>
+        <v>-0.05057619817857784</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.03942916747048986</v>
+        <v>0.3756402276831903</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9121690582271763</v>
+        <v>0.1632378494964285</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2826185422289196</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2192818557222349</v>
+        <v>0.3039907952816518</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2068834690314009</v>
+        <v>-0.1517821321501123</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4080952968553129</v>
+        <v>0.5657431775791431</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1285213228736198</v>
+        <v>-0.07611122125507053</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1530700202232739</v>
+        <v>0.198747981851543</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.01955550715997778</v>
+        <v>0.3493382847994992</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.169314496533993</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.1179464312207212</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.07853218117734195</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.0427733331954423</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.8811234607151575</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.1500721998113352</v>
-      </c>
+        <v>-0.1116030758516073</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7158,7 +6435,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7189,62 +6466,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.2380398983964456</v>
+        <v>0.07790371755156777</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1668426208539695</v>
+        <v>0.01591556172396702</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.05142325442912488</v>
+        <v>0.1326921036499702</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1154607916375272</v>
+        <v>0.182346219726028</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9239766081871345</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.05057619817857784</v>
+        <v>-0.2374052086143446</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3756402276831903</v>
+        <v>0.1049397228500237</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1632378494964285</v>
+        <v>0.7662401902298601</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3039907952816518</v>
+        <v>0.4134685021818567</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1517821321501123</v>
+        <v>-0.08056924670644672</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.5657431775791431</v>
+        <v>0.7694870630425669</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07611122125507053</v>
+        <v>-0.09083171626673225</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.198747981851543</v>
+        <v>0.04369407457614072</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3493382847994992</v>
+        <v>0.08381351492481048</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1116030758516073</v>
+        <v>-0.03701692200383122</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7260,7 +6537,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7278,91 +6555,85 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.07790371755156777</v>
+        <v>0.1434436149079494</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01591556172396702</v>
+        <v>0.07768638647757431</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2376588811135018</v>
+        <v>-0.07611122125507064</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1326921036499702</v>
+        <v>0.01299867294183905</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.182346219726028</v>
+        <v>0.06482391622384889</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.2319688109161793</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2374052086143446</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1049397228500237</v>
+        <v>0.465299433644307</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7662401902298601</v>
+        <v>-0.036483651193696</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2376588811135018</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4134685021818567</v>
+        <v>0.1306628532906307</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.08056924670644672</v>
+        <v>-0.2645282174188184</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7694870630425669</v>
+        <v>0.2431705793713567</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.07611122125507064</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.04369407457614072</v>
+        <v>0.1071539192778188</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.08381351492481048</v>
+        <v>0.4372832261827635</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03701692200383122</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.08697779648367798</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.02045620018255823</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.1096775832650454</v>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+        <v>-0.2296898070547482</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.1877889693631971</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.1579827546099043</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7372,7 +6643,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7403,62 +6674,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1434436149079494</v>
+        <v>0.01695327757228604</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.07768638647757431</v>
+        <v>-0.04152973646048097</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.07611122125507064</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.01299867294183905</v>
+        <v>0.120962550033912</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.06482391622384889</v>
+        <v>0.1697143146176368</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.2319688109161793</v>
+        <v>0.9961013645224172</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.2214796402899178</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.465299433644307</v>
+        <v>0.128014615636332</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.036483651193696</v>
+        <v>0.7148394203240476</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1306628532906307</v>
+        <v>0.3062642034833811</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2645282174188184</v>
+        <v>-0.1503033291826368</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2431705793713567</v>
+        <v>0.5699741121993481</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07611122125507064</v>
+        <v>-0.09083171626673225</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1071539192778188</v>
+        <v>-0.01532196926280427</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4372832261827635</v>
+        <v>0.1064472207641982</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2296898070547482</v>
+        <v>-0.1100542237730052</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -7467,122 +6738,6 @@
         <v>0.1877889693631971</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.1579827546099043</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.01695327757228604</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.04152973646048097</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.120962550033912</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1697143146176368</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9961013645224172</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2214796402899178</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.128014615636332</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7148394203240476</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.3062642034833811</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1503033291826368</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.5699741121993481</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.09083171626673225</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.01532196926280427</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.1064472207641982</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.1100542237730052</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.02551425956047315</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.02551425956047315</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.1877889693631971</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>-0.07570585866239699</v>
       </c>
     </row>
@@ -7597,7 +6752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7982,7 +7137,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7992,7 +7147,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8003,74 +7158,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.0520480753590512</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04977130173806421</v>
+        <v>0.01733422320252109</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0653683722520295</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2161775406597309</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1284458931702925</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5555413873337464</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.2152266720452527</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.03198399714010956</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.01791805706482619</v>
+        <v>0.05143695656071312</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.09116441700638167</v>
+        <v>0.2535130943000159</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.09996887029223012</v>
+        <v>-0.1612078395177402</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1307501836098439</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8080,7 +7243,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8111,62 +7274,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.0520480753590512</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.04977130173806421</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.0653683722520295</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2161775406597309</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1284458931702925</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5555413873337464</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.08282053666881062</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1579315375127712</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.289677927852336</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.04770979298828082</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.05143695656071312</v>
+        <v>-0.01791805706482619</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2535130943000159</v>
+        <v>0.09116441700638167</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1612078395177402</v>
+        <v>-0.09996887029223012</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -8175,7 +7338,7 @@
         <v>0.1692510023843161</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1307501836098439</v>
+        <v>-0.08068656438877009</v>
       </c>
     </row>
     <row r="6">
@@ -8186,7 +7349,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8204,94 +7367,84 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.0520480753590512</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04977130173806421</v>
+        <v>0.01733422320252109</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0653683722520295</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2161775406597309</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1284458931702925</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5555413873337464</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.2152266720452527</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.03198399714010956</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.01791805706482619</v>
+        <v>0.05143695656071312</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.09116441700638167</v>
+        <v>0.2535130943000159</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.09996887029223012</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.1612078395177402</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.04615004753547058</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.08068656438877009</v>
+        <v>-0.03928937762398355</v>
       </c>
     </row>
     <row r="7">
@@ -8302,7 +7455,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8333,62 +7486,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.0520480753590512</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.04977130173806421</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.0653683722520295</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2161775406597309</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1284458931702925</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5555413873337464</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.08282053666881062</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1579315375127712</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.289677927852336</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.04770979298828082</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.05143695656071312</v>
+        <v>-0.01791805706482619</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2535130943000159</v>
+        <v>0.09116441700638167</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1612078395177402</v>
+        <v>-0.09996887029223012</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -8397,7 +7550,7 @@
         <v>0.04615004753547058</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.03928937762398355</v>
+        <v>0.02142863298018183</v>
       </c>
     </row>
     <row r="8">
@@ -8408,7 +7561,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8426,94 +7579,84 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.0520480753590512</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.04977130173806421</v>
+        <v>0.01733422320252109</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.0653683722520295</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2161775406597309</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1284458931702925</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5555413873337464</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.2152266720452527</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.03198399714010956</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01791805706482619</v>
+        <v>0.05143695656071312</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.09116441700638167</v>
+        <v>0.2535130943000159</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.09996887029223012</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.1612078395177402</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
-        <v>0.04615004753547058</v>
+        <v>0.1692510023843161</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.02142863298018183</v>
+        <v>-0.1307501836098439</v>
       </c>
     </row>
     <row r="9">
@@ -8524,7 +7667,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8555,62 +7698,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.0520480753590512</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.04977130173806421</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.0653683722520295</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2161775406597309</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1284458931702925</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5555413873337464</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.08282053666881062</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1579315375127712</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.289677927852336</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.04770979298828082</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.05143695656071312</v>
+        <v>-0.01791805706482619</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.2535130943000159</v>
+        <v>0.09116441700638167</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1612078395177402</v>
+        <v>-0.09996887029223012</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -8619,122 +7762,6 @@
         <v>0.1692510023843161</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.1307501836098439</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.0520480753590512</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.04977130173806421</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.0653683722520295</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2161775406597309</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1284458931702925</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5555413873337464</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.08282053666881062</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1579315375127712</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.289677927852336</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.04770979298828082</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.01791805706482619</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.09116441700638167</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.09996887029223012</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.1692510023843161</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>-0.08068656438877009</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>1.258981438936668</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -966,19 +967,19 @@
         <v>1.139014180044933</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
@@ -986,7 +987,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -994,19 +995,19 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1014,7 +1015,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1103,27 +1104,27 @@
         <v>1.304320163452614</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1131,27 +1132,27 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1240,19 +1241,19 @@
         <v>1.870237883382897</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
@@ -1260,7 +1261,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1268,19 +1269,19 @@
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1288,7 +1289,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr"/>
@@ -1377,27 +1378,27 @@
         <v>1.798433611188803</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1405,27 +1406,27 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1514,19 +1515,19 @@
         <v>1.92758584033941</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
@@ -1534,7 +1535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1542,19 +1543,19 @@
       </c>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr"/>
@@ -1651,27 +1652,27 @@
         <v>1.836146217807533</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1679,27 +1680,27 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1950,28 +1951,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766695</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208211</v>
+        <v>0.08831268540851211</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997945</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798214</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -1980,10 +1981,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278878</v>
+        <v>0.272403402144199</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -1992,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.139529174066894</v>
+        <v>-0.08310591627222996</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2038,49 +2039,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.1406064183528005</v>
+        <v>0.03065849396422626</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.05203685476090714</v>
+        <v>-0.02440421607187349</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.5405779751541202</v>
+        <v>-0.1840536062106816</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.3325799988927458</v>
+        <v>0.0958017749538176</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1798617631710739</v>
+        <v>0.3109311052344195</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5086297155507329</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.07208292313732823</v>
+        <v>0.0009345351247636025</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.081135417924184</v>
+        <v>0.9954284811619402</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.5405779751541202</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7489734500538974</v>
+        <v>0.2401923912366097</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.02160329718706966</v>
+        <v>-0.02531509335271243</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.051945482042245</v>
+        <v>0.8817525381326254</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1427514496479956</v>
+        <v>-0.1050869895001562</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2140,58 +2141,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.09180870584028344</v>
+        <v>-0.1380515322508087</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.2043310968229539</v>
+        <v>-0.1841009451491431</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2212307393619097</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1451694086489946</v>
+        <v>0.1162855119534902</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1041195199922966</v>
+        <v>0.2802072296625115</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9756232686980609</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1676178254853798</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.5718932516928532</v>
+        <v>0.0009345351247636025</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.3562858446275809</v>
+        <v>0.9954284811619402</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2212307393619097</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3116675720223592</v>
+        <v>0.03718344883470714</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2338340434212389</v>
+        <v>-0.1848627195692101</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4377422113753213</v>
+        <v>0.1365014112967054</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07218203518241495</v>
+        <v>-0.06481729796712832</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.2704408424224136</v>
+        <v>-0.1636914916075884</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.6940018573723128</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2500357441206794</v>
+        <v>-0.1636914916075884</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2242,58 +2243,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1072953106862609</v>
+        <v>0.0455130560312218</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2214137594729695</v>
+        <v>-0.01034325581245854</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.4324281870017384</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2036681684298383</v>
+        <v>0.08576028584916257</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1621472165416299</v>
+        <v>0.306967969256086</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9789473684210527</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3804356199995604</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1700023111137057</v>
+        <v>0.0009345351247636025</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8086480408957659</v>
+        <v>0.9954284811619402</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.4324281870017384</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.7872158994767828</v>
+        <v>0.2580669005513112</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.04394132205630119</v>
+        <v>-0.01126726128579081</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.105657628834282</v>
+        <v>0.9473703284171956</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.06483897573256081</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.288461229328602</v>
+        <v>0.01441269067687045</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2608910217166545</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.02186565463398371</v>
+        <v>0.01441269067687045</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2344,58 +2345,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.3166303960343169</v>
+        <v>-0.1380515322508087</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2462019580196928</v>
+        <v>-0.1841009451491431</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.6167647998119878</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.441784976019348</v>
+        <v>0.1162855119534902</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1668707085500485</v>
+        <v>0.2802072296625115</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.5651990807842828</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1789100587796997</v>
+        <v>0.0009345351247636025</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.201378381427129</v>
+        <v>0.9954284811619402</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.6167647998119878</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5716838989170674</v>
+        <v>0.03718344883470714</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08195435830085074</v>
+        <v>-0.1848627195692101</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.802939402696889</v>
+        <v>0.1365014112967054</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1220228475473601</v>
+        <v>-0.06481729796712832</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.2048234725515767</v>
+        <v>-0.1636914916075884</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.1151257351611188</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1013677772703563</v>
+        <v>-0.1636914916075884</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -2446,58 +2447,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1509545937884657</v>
+        <v>0.0455130560312218</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.06345151870880028</v>
+        <v>-0.01034325581245854</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.5687081783665724</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.3453849329396694</v>
+        <v>0.08576028584916257</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1761679438089752</v>
+        <v>0.306967969256086</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.5252150592986788</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1034031396347619</v>
+        <v>0.0009345351247636025</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.116388966814729</v>
+        <v>0.9954284811619402</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.5687081783665724</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7882736654565754</v>
+        <v>0.2580669005513112</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.04455918004183834</v>
+        <v>-0.01126726128579081</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.107143278483707</v>
+        <v>0.9473703284171956</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1229482572702627</v>
+        <v>-0.06483897573256081</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.01204125287488278</v>
+        <v>0.01441269067687045</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.03375324937798174</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.02247044710796886</v>
+        <v>0.01441269067687045</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2548,64 +2549,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.03531692510718976</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.06410383014673715</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3860586751023685</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2627667438659022</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1170982492244087</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9955678670360111</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3482013611471607</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.2308743666607311</v>
+        <v>0.2117597153840087</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.740131401284706</v>
+        <v>-0.03587709265072071</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3814494404070007</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4800323556837203</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1354894870111152</v>
+        <v>-0.2060850325577076</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6742133085748864</v>
+        <v>0.03737143334716841</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07218203518241484</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1225160339734006</v>
+        <v>-0.01390084824531057</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3264917710345101</v>
+        <v>0.2106283406766121</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1537708273169551</v>
+        <v>-0.185465003071409</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.04814722243458536</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.04405046681985514</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2650,64 +2655,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.03485048027329096</v>
+        <v>0.06577286665514515</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.1415027259707617</v>
+        <v>0.008834178753532651</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4958240313246576</v>
+        <v>-0.1588454086617709</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.252789065656861</v>
+        <v>0.07957894723870008</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1629974290144591</v>
+        <v>0.2697343811059919</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9933518005540166</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4284675262734969</v>
+        <v>-0.1588454086617709</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.07929754634388031</v>
+        <v>0.01310805774796986</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9107439143288391</v>
+        <v>0.935878565355825</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4958240313246576</v>
+        <v>-0.1588454086617709</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.8106591101042158</v>
+        <v>0.2670356645852237</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.0576348754220759</v>
+        <v>-0.004218581583427028</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.13858400226223</v>
+        <v>0.980294895303349</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.04142921346750827</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.2041636130092959</v>
+        <v>0.03406984262639545</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1631400835870296</v>
+        <v>0.01216215666061404</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.03526963776861081</v>
+        <v>0.02164444286087597</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.04814722243458536</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.01572483169298367</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2950,28 +2959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05341499464255506</v>
+        <v>-0.09123360655355239</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360366</v>
+        <v>0.2716992530341484</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019927</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4707583434268603</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2980,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.12172130237064</v>
+        <v>0.7171104771509207</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2992,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756415</v>
+        <v>-0.139529174066894</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3038,49 +3047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.2807829634843186</v>
+        <v>-0.1441435513209015</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.2158389333720412</v>
+        <v>-0.05822172248985902</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4486552572799976</v>
+        <v>-0.5405779751541202</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1673128535837262</v>
+        <v>0.3327436642745257</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2148728007780382</v>
+        <v>0.179942036489818</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9476744186046512</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4418768397766435</v>
+        <v>-0.5118569259989467</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1241360759195709</v>
+        <v>-0.07765560790925141</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8775942790903688</v>
+        <v>1.087302929721673</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4486552572799976</v>
+        <v>-0.5405779751541202</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.294803467700139</v>
+        <v>0.7532901607393325</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.08157629615921302</v>
+        <v>0.0210700965778523</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.154300506697793</v>
+        <v>1.050452035971018</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1198660820476312</v>
+        <v>-0.1427514496479956</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3140,68 +3149,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.05330476645442528</v>
+        <v>0.0844348229128784</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.0001046389017532734</v>
+        <v>0.1933042757008407</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1365494988551755</v>
+        <v>-0.2212307393619097</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04436078156857341</v>
+        <v>0.1452478190196952</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.07838093185860415</v>
+        <v>0.1041485359598032</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.3561046511627907</v>
+        <v>0.9761508596783139</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.1730847259787854</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1.058870045499049</v>
+        <v>0.5624531133386648</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.04411026616389809</v>
+        <v>0.3676721366610826</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2212307393619097</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.03041923040339545</v>
+        <v>0.3114219279556532</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.5143475114982876</v>
+        <v>-0.2362623457218651</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.02711834957498587</v>
+        <v>0.4342732924401442</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1365494988551758</v>
+        <v>-0.07218203518241495</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.1776086999244962</v>
+        <v>0.2670755996365517</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.8315131856388851</v>
+        <v>0.6940018573723128</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.5509771338126459</v>
+        <v>-0.2520223079318207</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.1475930532307546</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.1079725986742808</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3246,68 +3251,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3169134849931055</v>
+        <v>0.1015024337241781</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2501374023444205</v>
+        <v>0.2120853518215935</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4324281870017382</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1173744075779711</v>
+        <v>0.2037810327998786</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2016898091529489</v>
+        <v>0.1622179260057351</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9375</v>
+        <v>0.9794786466999446</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3845047806789035</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2739414126958895</v>
+        <v>0.1629757629179305</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7298771057515232</v>
+        <v>0.8167774104223441</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4324281870017382</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.082076248570495</v>
+        <v>0.7896198039347198</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01868532580402937</v>
+        <v>0.04222752568845123</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9646569484627249</v>
+        <v>1.101113188405612</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1198660820476311</v>
+        <v>-0.1156623821440808</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.02820971432231989</v>
+        <v>0.2870177416133299</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1332626360681237</v>
+        <v>0.2608910217166545</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.09269953707314182</v>
+        <v>0.02072083903104072</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1475930532307546</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.007539848144645811</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3352,58 +3353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3454968097333002</v>
+        <v>-0.3194430411450147</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2772713665328586</v>
+        <v>-0.2511200196631285</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2347571285205642</v>
+        <v>-0.6167647998119878</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0619851418071798</v>
+        <v>0.4419615127159511</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1352481678306468</v>
+        <v>0.1669417848932911</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9418604651162791</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2253489755584758</v>
+        <v>-0.5680547562571263</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.5602526913132901</v>
+        <v>-0.1838411841204339</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.4475567713595454</v>
+        <v>1.206680166562746</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2347571285205642</v>
+        <v>-0.6167647998119878</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7369070294631324</v>
+        <v>0.5755630342352009</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1813689066879554</v>
+        <v>-0.08243350954947248</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6569430641156202</v>
+        <v>0.8026141753247176</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1365494988551768</v>
+        <v>-0.1220228475473601</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.05052678564128477</v>
+        <v>-0.2048234725515766</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3879571385848151</v>
+        <v>-0.1151257351611187</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2431129489254835</v>
+        <v>-0.1013677772703562</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -3454,58 +3455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4287589137569821</v>
+        <v>-0.1544491352440456</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3563115401084533</v>
+        <v>-0.0695619128814301</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3717086876431007</v>
+        <v>-0.5687081783665724</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1130847159364414</v>
+        <v>0.3455538151157958</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.207610581704922</v>
+        <v>0.1762457357820641</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9236918604651163</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3639842631607436</v>
+        <v>-0.5283333409078388</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2810223362661595</v>
+        <v>-0.1087877281878733</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.722894884443944</v>
+        <v>1.1223026597083</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3717086876431007</v>
+        <v>-0.5687081783665724</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.246420695276098</v>
+        <v>0.792687374561148</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.05877274869518856</v>
+        <v>0.04401399817653351</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.111167892275843</v>
+        <v>1.105390870470188</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1198660820476312</v>
+        <v>-0.1229482572702627</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1155355391908874</v>
+        <v>-0.01204125287488267</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1395616275531872</v>
+        <v>-0.03375324937798163</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.02108362354556237</v>
+        <v>0.02247044710796886</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3556,58 +3557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2397270581692568</v>
+        <v>-0.03928741357817911</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1768648296011024</v>
+        <v>0.05716121695298404</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1198660820476312</v>
+        <v>-0.3860586751023684</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04797087557380604</v>
+        <v>0.2629055615097304</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1081360511451568</v>
+        <v>0.1171335657874987</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9106104651162791</v>
+        <v>0.9961175818080976</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.008209339511976887</v>
+        <v>-0.352482229250113</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.9976014985088748</v>
+        <v>0.2234822461682056</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.01630424756921656</v>
+        <v>0.7487540776956545</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.06689328315495324</v>
+        <v>-0.3814494404070007</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2499886392953465</v>
+        <v>0.4836852821957682</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.4108610598862772</v>
+        <v>-0.1359406969215273</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.2228616312866858</v>
+        <v>0.6744920031254451</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1198660820476312</v>
+        <v>-0.07218203518241484</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03205531810274154</v>
+        <v>0.1225160339734006</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.7770104005200507</v>
+        <v>0.3264917710345101</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.455295995108422</v>
+        <v>-0.153770827316955</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -3658,58 +3659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.476378731544906</v>
+        <v>0.03059119345872818</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.4015167232794812</v>
+        <v>0.1340551333002826</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3639469600214459</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1121637776951362</v>
+        <v>0.2529285752428129</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2042768068824445</v>
+        <v>0.1630666974872854</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9236918604651163</v>
+        <v>0.9938990571270105</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3561271102519857</v>
+        <v>-0.4322212241039853</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2968477125777542</v>
+        <v>0.07281573331246127</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7072901008889843</v>
+        <v>0.9181382128198811</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3639469600214459</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1.292966135167922</v>
+        <v>0.8151280696118781</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.08071033297631836</v>
+        <v>0.0570828690205134</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.152662548562976</v>
+        <v>1.136684089249931</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1198660820476313</v>
+        <v>-0.1156623821440808</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1527157790485258</v>
+        <v>0.2041636130092959</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1536394395286185</v>
+        <v>0.1631400835870296</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.000800649187643665</v>
+        <v>0.03526963776861081</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -3958,28 +3959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.05341499464255506</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702572</v>
+        <v>0.2216991067360366</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962868</v>
+        <v>0.2389480542019927</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3988,10 +3989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.12172130237064</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4000,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756415</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4046,49 +4047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.005584530641855379</v>
+        <v>0.2807829634843186</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.01741759632229589</v>
+        <v>0.2158389333720412</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.4486552572799976</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.07919440518124658</v>
+        <v>0.1673128535837262</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2118816077559385</v>
+        <v>0.2148728007780382</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9476744186046512</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.4418768397766435</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.003021666415692792</v>
+        <v>0.1241360759195709</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9875605795415207</v>
+        <v>0.8775942790903688</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.4486552572799976</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2460863607380916</v>
+        <v>1.294803467700139</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.02037768816203989</v>
+        <v>0.08157629615921302</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9047062469143489</v>
+        <v>1.154300506697793</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.03283822635553391</v>
+        <v>-0.1198660820476312</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4148,67 +4149,67 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0008500212579751754</v>
+        <v>0.05330476645442528</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.02204380671922623</v>
+        <v>-0.0001046389017532734</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1971519721341342</v>
+        <v>-0.1365494988551755</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07990143847314349</v>
+        <v>0.04436078156857341</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2116131333080739</v>
+        <v>0.07838093185860415</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.3561046511627907</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1968052513911284</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.001700776449303554</v>
+        <v>1.058870045499049</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.00700165751219</v>
+        <v>-0.04411026616389809</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1971519721341342</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2460863607380914</v>
+        <v>0.03041923040339545</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.02037768816204011</v>
+        <v>-0.5143475114982876</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.9047062469143481</v>
+        <v>0.02711834957498587</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.03283822635553379</v>
+        <v>-0.1365494988551758</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.004708216206208204</v>
+        <v>-0.1776086999244962</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>-0.004708216206208093</v>
+        <v>0.8315131856388851</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-0.5509771338126459</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>0.2004725031597112</v>
+        <v>0.1475930532307546</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>-0.1592411666562514</v>
+        <v>-0.1079725986742808</v>
       </c>
     </row>
     <row r="5">
@@ -4254,67 +4255,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.006391146990712304</v>
+        <v>0.3169134849931055</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.02911933770287078</v>
+        <v>0.2501374023444205</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0852684684349431</v>
+        <v>0.1173744075779711</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2120594124587969</v>
+        <v>0.2016898091529489</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2026163801193158</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.008923489629824699</v>
+        <v>0.2739414126958895</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.036735702818083</v>
+        <v>0.7298771057515232</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2460863607380916</v>
+        <v>1.082076248570495</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.02037768816203989</v>
+        <v>-0.01868532580402937</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9047062469143489</v>
+        <v>0.9646569484627249</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.03283822635553391</v>
+        <v>-0.1198660820476311</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.01190917050496365</v>
+        <v>0.02820971432231989</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-0.01190917050496387</v>
+        <v>0.1332626360681237</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.09269953707314182</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.2004725031597112</v>
+        <v>0.1475930532307546</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.01980775507866428</v>
+        <v>-0.007539848144645811</v>
       </c>
     </row>
     <row r="6">
@@ -4360,58 +4361,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.1018000785001284</v>
+        <v>0.3454968097333002</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1223458486506929</v>
+        <v>0.2772713665328586</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.2347571285205642</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1102282466387932</v>
+        <v>0.0619851418071798</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1849974711385499</v>
+        <v>0.1352481678306468</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9418604651162791</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.2253489755584758</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.003021666415692792</v>
+        <v>0.5602526913132901</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9875605795415207</v>
+        <v>0.4475567713595454</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.2347571285205642</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1130189827826977</v>
+        <v>0.7369070294631324</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1249898374721931</v>
+        <v>-0.1813689066879554</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4155003935883911</v>
+        <v>0.6569430641156202</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.006326442692099143</v>
+        <v>-0.1365494988551768</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.106788246904953</v>
+        <v>0.05052678564128477</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.3879571385848151</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1067882469049533</v>
+        <v>-0.2431129489254835</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -4462,58 +4463,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.03281284150392505</v>
+        <v>0.4287589137569821</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05493665222287392</v>
+        <v>0.3563115401084533</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.3717086876431007</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.08741987364983472</v>
+        <v>0.1130847159364414</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.198908108056075</v>
+        <v>0.207610581704922</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9236918604651163</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.3639842631607436</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.003021666415692792</v>
+        <v>0.2810223362661595</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9875605795415207</v>
+        <v>0.722894884443944</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.3717086876431007</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1985056350396743</v>
+        <v>1.246420695276098</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.05778371552598793</v>
+        <v>0.05877274869518856</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7297815593251392</v>
+        <v>1.111167892275843</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02015312857781415</v>
+        <v>-0.1198660820476312</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.03818413169231205</v>
+        <v>0.1155355391908874</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.1395616275531872</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.03818413169231216</v>
+        <v>-0.02108362354556237</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4564,58 +4565,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.1018000785001288</v>
+        <v>0.2397270581692568</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1223458486506933</v>
+        <v>0.1768648296011024</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.196417529389515</v>
+        <v>-0.1198660820476312</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1102282466387935</v>
+        <v>0.04797087557380604</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1849974711385499</v>
+        <v>0.1081360511451568</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9106104651162791</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1930057479754297</v>
+        <v>-0.008209339511976887</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.00302166641569257</v>
+        <v>0.9976014985088748</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9875605795415218</v>
+        <v>0.01630424756921656</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.196417529389515</v>
+        <v>-0.06689328315495324</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1130189827826975</v>
+        <v>0.2499886392953465</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1249898374721933</v>
+        <v>-0.4108610598862772</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.4155003935883903</v>
+        <v>0.2228616312866858</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.006326442692098921</v>
+        <v>-0.1198660820476312</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.1067882469049535</v>
+        <v>-0.03205531810274154</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0.7770104005200507</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1067882469049534</v>
+        <v>-0.455295995108422</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -4666,58 +4667,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.03281284150392505</v>
+        <v>0.476378731544906</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.05493665222287392</v>
+        <v>0.4015167232794812</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.3639469600214459</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.08741987364983472</v>
+        <v>0.1121637776951362</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.198908108056075</v>
+        <v>0.2042768068824445</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9236918604651163</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.3561271102519857</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.003021666415692792</v>
+        <v>0.2968477125777542</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9875605795415207</v>
+        <v>0.7072901008889843</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.3639469600214459</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1985056350396743</v>
+        <v>1.292966135167922</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.05778371552598793</v>
+        <v>0.08071033297631836</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7297815593251392</v>
+        <v>1.152662548562976</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.02015312857781415</v>
+        <v>-0.1198660820476313</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.03818413169231205</v>
+        <v>0.1527157790485258</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.1536394395286185</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.03818413169231216</v>
+        <v>-0.000800649187643665</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4966,28 +4967,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.0189121018756262</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.0809929380075199</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4590501973559848</v>
+        <v>0.2138559415886582</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4996,10 +4997,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5008,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.0518515658788602</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5054,49 +5055,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.03653107044182335</v>
+        <v>0.003018060423530589</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.05583341556643984</v>
+        <v>-0.01559903098887294</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1224269746777639</v>
+        <v>0.07892753856493077</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4598626791204086</v>
+        <v>0.2111772154448013</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02087617766040506</v>
+        <v>0.004878060774464288</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.051056167955528</v>
+        <v>0.9803618455261432</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4914912653967582</v>
+        <v>0.2460863607380916</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.03570257112374731</v>
+        <v>-0.02037768816203989</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8989933696214515</v>
+        <v>0.9047062469143489</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.06498956817109347</v>
+        <v>-0.03283822635553391</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5156,64 +5157,68 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.2393739026337791</v>
+        <v>0.0009353369301576819</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.307152708818292</v>
+        <v>-0.01764309689950361</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.197151972134134</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.2264340196757501</v>
+        <v>0.07962920109406921</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4091073817733869</v>
+        <v>0.2108821961739259</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.196736784489579</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.02087617766040484</v>
+        <v>0.00279147507104649</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.051056167955527</v>
+        <v>0.9887620468071862</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.197151972134134</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.09448449043690843</v>
+        <v>0.2460863607380914</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2923803145488134</v>
+        <v>-0.02037768816204011</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.172822868716239</v>
+        <v>0.9047062469143481</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.06547477152419368</v>
+        <v>-0.03283822635553379</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.2661810928233896</v>
+        <v>-0.002076456621821432</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.002076456621820988</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.26618109282339</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.2035442094916755</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1614584458581432</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5258,64 +5263,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.03040624665895153</v>
+        <v>-0.004119828020561656</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1168059998530311</v>
+        <v>-0.02260443256468381</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.2026163801193158</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1399077070334797</v>
+        <v>0.08497794469960135</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4555303123429243</v>
+        <v>0.2113490304617309</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.2007936180365936</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02087617766040506</v>
+        <v>-0.002273064196002483</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.051056167955528</v>
+        <v>1.009150928591084</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.2026163801193158</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3951734350568115</v>
+        <v>0.2460863607380916</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.09797516923181782</v>
+        <v>-0.02037768816203989</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7228171139111152</v>
+        <v>0.9047062469143489</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0854476532288605</v>
+        <v>-0.03283822635553391</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.06457820610456255</v>
+        <v>-0.007116410686641261</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>-0.00711641068664115</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.06457820610456266</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.2035442094916755</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.02453925236218701</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5360,58 +5369,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.2393739026337792</v>
+        <v>-0.1040924798631048</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3071527088182922</v>
+        <v>-0.1207214847211086</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2264340196757502</v>
+        <v>0.1098548087600672</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.409107381773387</v>
+        <v>0.1843738661552207</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02087617766040506</v>
+        <v>0.004878060774464288</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.051056167955528</v>
+        <v>0.9803618455261432</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.09448449043690843</v>
+        <v>0.1130189827826977</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2923803145488134</v>
+        <v>-0.1249898374721931</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.172822868716239</v>
+        <v>0.4155003935883911</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.06547477152419368</v>
+        <v>-0.006326442692099143</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.2661810928233898</v>
+        <v>-0.1067882469049533</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.26618109282339</v>
+        <v>-0.1067882469049533</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -5462,58 +5471,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.03040624665895153</v>
+        <v>-0.03528131328544915</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1168059998530311</v>
+        <v>-0.05318752722763365</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1399077070334797</v>
+        <v>0.0871247028361211</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4555303123429243</v>
+        <v>0.1982445728101207</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02087617766040506</v>
+        <v>0.004878060774464288</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.051056167955528</v>
+        <v>0.9803618455261432</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3951734350568115</v>
+        <v>0.1985056350396743</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.09797516923181782</v>
+        <v>-0.05778371552598793</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7228171139111152</v>
+        <v>0.7297815593251392</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.0854476532288605</v>
+        <v>-0.02015312857781415</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.06457820610456255</v>
+        <v>-0.03818413169231227</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.06457820610456266</v>
+        <v>-0.03818413169231216</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5564,58 +5573,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.2393739026337796</v>
+        <v>-0.1040924798631052</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3071527088182925</v>
+        <v>-0.120721484721109</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2264340196757505</v>
+        <v>0.1098548087600675</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4091073817733872</v>
+        <v>0.1843738661552208</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.1950653726524904</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02087617766040561</v>
+        <v>0.004878060774464066</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.051056167955529</v>
+        <v>0.9803618455261438</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.09448449043690865</v>
+        <v>0.1130189827826975</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2923803145488132</v>
+        <v>-0.1249898374721933</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.1728228687162394</v>
+        <v>0.4155003935883903</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0654747715241939</v>
+        <v>-0.006326442692098921</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.2661810928233901</v>
+        <v>-0.1067882469049537</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-6.661338147750939e-16</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.2661810928233898</v>
+        <v>-0.1067882469049534</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -5666,58 +5675,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.03040624665895153</v>
+        <v>-0.03528131328544915</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1168059998530311</v>
+        <v>-0.05318752722763365</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1399077070334797</v>
+        <v>0.0871247028361211</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4555303123429243</v>
+        <v>0.1982445728101207</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.02087617766040506</v>
+        <v>0.004878060774464288</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.051056167955528</v>
+        <v>0.9803618455261432</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3951734350568115</v>
+        <v>0.1985056350396743</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.09797516923181782</v>
+        <v>-0.05778371552598793</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7228171139111152</v>
+        <v>0.7297815593251392</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0854476532288605</v>
+        <v>-0.02015312857781415</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.06457820610456255</v>
+        <v>-0.03818413169231227</v>
       </c>
       <c r="Z9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.06457820610456266</v>
+        <v>-0.03818413169231216</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5966,28 +5975,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393833</v>
+        <v>0.1113578145363061</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.179974191375289</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.451830499217423</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450096</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5996,10 +6005,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241683001</v>
+        <v>0.5657770181230009</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6008,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.0518515658788602</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6054,49 +6063,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.03277746210192878</v>
+        <v>0.04820889971753206</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.02661557014535587</v>
+        <v>-0.05682140710471517</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2991318266089934</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1728680437397538</v>
+        <v>0.120483568435348</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2051485421432778</v>
+        <v>0.4525656398613154</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.98635477582846</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2963782229283601</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.01949247507462459</v>
+        <v>-0.02087617766040506</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9565792900758322</v>
+        <v>1.051056167955528</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2963782229283602</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4678020148838795</v>
+        <v>0.5082947948424215</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.0452264693926312</v>
+        <v>-0.0367116279107782</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8706046448976331</v>
+        <v>0.8984012756981892</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.09352882951066699</v>
+        <v>-0.06498956817109347</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6156,68 +6165,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.1528517297824459</v>
+        <v>-0.239361358658418</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.2015695866079242</v>
+        <v>-0.3155771872995335</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2645312178855237</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.2010923836949493</v>
+        <v>0.2268525685166392</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1705899623566641</v>
+        <v>0.4025574048720759</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.8791423001949318</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2519196755963159</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.08390940464494601</v>
+        <v>-0.02087617766040484</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.8130865421117908</v>
+        <v>1.051056167955527</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2618497648763229</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1324295568030611</v>
+        <v>0.09450254028627425</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2633790149153505</v>
+        <v>-0.3009844137332365</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.2464585093826474</v>
+        <v>0.1670314227322136</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.09105587445754815</v>
+        <v>-0.06547477152419368</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.1797378415932688</v>
+        <v>-0.2743444159398414</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.06318529184396993</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2284861682161884</v>
+        <v>-0.2743444159398415</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.8811234607151575</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.4676866206072701</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6262,19 +6267,19 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.1253098049081549</v>
+        <v>-0.02780133112833449</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1756115445082261</v>
+        <v>-0.1252154291304481</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3130106839482674</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2047087134872211</v>
+        <v>0.1378064886050969</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.190171927237105</v>
+        <v>0.4482930115011555</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -6283,47 +6288,43 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2826185422289195</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.03942916747048986</v>
+        <v>-0.02087617766040506</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9121690582271763</v>
+        <v>1.051056167955528</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2826185422289196</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2192818557222349</v>
+        <v>0.3989217151342774</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2068834690314009</v>
+        <v>-0.1065638983440591</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.4080952968553129</v>
+        <v>0.7050864604888408</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1285213228736198</v>
+        <v>-0.0854476532288605</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1530700202232739</v>
+        <v>-0.0725143918033414</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.01955550715997778</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.169314496533993</v>
+        <v>-0.07251439180334152</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.8811234607151575</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.1500721998113352</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6368,58 +6369,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2380398983964456</v>
+        <v>-0.2393613586584181</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1668426208539695</v>
+        <v>-0.3155771872995337</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.05142325442912488</v>
+        <v>0.2268525685166394</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1154607916375272</v>
+        <v>0.402557404872076</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9239766081871345</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.05057619817857784</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.3756402276831903</v>
+        <v>-0.02087617766040506</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.1632378494964285</v>
+        <v>1.051056167955528</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3039907952816518</v>
+        <v>0.09450254028627425</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1517821321501123</v>
+        <v>-0.3009844137332365</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.5657431775791431</v>
+        <v>0.1670314227322136</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07611122125507053</v>
+        <v>-0.06547477152419368</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.198747981851543</v>
+        <v>-0.2743444159398415</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3493382847994992</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1116030758516073</v>
+        <v>-0.2743444159398415</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -6470,58 +6471,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.07790371755156777</v>
+        <v>-0.02780133112833449</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01591556172396702</v>
+        <v>-0.1252154291304481</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2376588811135018</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1326921036499702</v>
+        <v>0.1378064886050969</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.182346219726028</v>
+        <v>0.4482930115011555</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2374052086143446</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1049397228500237</v>
+        <v>-0.02087617766040506</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7662401902298601</v>
+        <v>1.051056167955528</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2376588811135018</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4134685021818567</v>
+        <v>0.3989217151342774</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.08056924670644672</v>
+        <v>-0.1065638983440591</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7694870630425669</v>
+        <v>0.7050864604888408</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.0854476532288605</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.04369407457614072</v>
+        <v>-0.0725143918033414</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.08381351492481048</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.03701692200383122</v>
+        <v>-0.07251439180334152</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6572,68 +6573,64 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1434436149079494</v>
+        <v>-0.2393613586584185</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.07768638647757431</v>
+        <v>-0.3155771872995339</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.07611122125507064</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.01299867294183905</v>
+        <v>0.2268525685166397</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.06482391622384889</v>
+        <v>0.4025574048720762</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2319688109161793</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.465299433644307</v>
+        <v>-0.02087617766040561</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.036483651193696</v>
+        <v>1.051056167955529</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1306628532906307</v>
+        <v>0.09450254028627447</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2645282174188184</v>
+        <v>-0.3009844137332364</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.2431705793713567</v>
+        <v>0.167031422732214</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07611122125507064</v>
+        <v>-0.0654747715241939</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1071539192778188</v>
+        <v>-0.2743444159398418</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.4372832261827635</v>
+        <v>-6.661338147750939e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.2296898070547482</v>
+        <v>-0.2743444159398414</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="n">
-        <v>0.1877889693631971</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.1579827546099043</v>
-      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6678,68 +6675,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.01695327757228604</v>
+        <v>-0.02780133112833449</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.04152973646048097</v>
+        <v>-0.1252154291304481</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.120962550033912</v>
+        <v>0.1378064886050969</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1697143146176368</v>
+        <v>0.4482930115011555</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9961013645224172</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2214796402899178</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.128014615636332</v>
+        <v>-0.02087617766040506</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7148394203240476</v>
+        <v>1.051056167955528</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3062642034833811</v>
+        <v>0.3989217151342774</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1503033291826368</v>
+        <v>-0.1065638983440591</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.5699741121993481</v>
+        <v>0.7050864604888408</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.0854476532288605</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.01532196926280427</v>
+        <v>-0.0725143918033414</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1064472207641982</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1100542237730052</v>
+        <v>-0.07251439180334152</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.1877889693631971</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.07570585866239699</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6982,28 +6975,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974344</v>
+        <v>0.06101703543393833</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252791</v>
+        <v>0.179974191375289</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005002</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450096</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7012,10 +7005,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922787</v>
+        <v>0.5373300241683001</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7024,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7070,49 +7063,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.0347527195054822</v>
+        <v>0.03277746210192878</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.0324344062146561</v>
+        <v>-0.02661557014535587</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1977751279185385</v>
+        <v>-0.2991318266089934</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.102894524153197</v>
+        <v>0.1728680437397538</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.278828778962905</v>
+        <v>0.2051485421432778</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.98635477582846</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1976947509848085</v>
+        <v>-0.2963782229283601</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.03416668980664972</v>
+        <v>0.01949247507462459</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8817737245150478</v>
+        <v>0.9565792900758322</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1977751279185385</v>
+        <v>-0.2963782229283602</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2030923163962011</v>
+        <v>0.4678020148838795</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.06440073604938645</v>
+        <v>-0.0452264693926312</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.710347502475649</v>
+        <v>0.8706046448976331</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.04392132259347603</v>
+        <v>-0.09352882951066699</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7172,67 +7165,67 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.1528517297824459</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.2015695866079242</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2645312178855237</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>0.2010923836949493</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1705899623566641</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0</v>
+        <v>0.8791423001949318</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2519196755963159</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.08390940464494601</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.8130865421117908</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2618497648763229</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1324295568030611</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2633790149153505</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.2464585093826474</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0</v>
+        <v>-0.09105587445754815</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.05143695656071312</v>
+        <v>-0.1797378415932688</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2535130943000159</v>
+        <v>0.06318529184396993</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1612078395177402</v>
+        <v>-0.2284861682161884</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.8811234607151575</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>-0.1307501836098439</v>
+        <v>-0.4676866206072701</v>
       </c>
     </row>
     <row r="5">
@@ -7278,19 +7271,19 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.0520480753590512</v>
+        <v>-0.1253098049081549</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.04977130173806421</v>
+        <v>-0.1756115445082261</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.3130106839482674</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0653683722520295</v>
+        <v>0.2047087134872211</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2161775406597309</v>
+        <v>0.190171927237105</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -7299,46 +7292,46 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2826185422289195</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1284458931702925</v>
+        <v>0.03942916747048986</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5555413873337464</v>
+        <v>0.9121690582271763</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2826185422289196</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.2192818557222349</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.2068834690314009</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.4080952968553129</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>-0.1285213228736198</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.01791805706482619</v>
+        <v>-0.1530700202232739</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.09116441700638167</v>
+        <v>0.01955550715997778</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.09996887029223012</v>
+        <v>-0.169314496533993</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.8811234607151575</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.08068656438877009</v>
+        <v>-0.1500721998113352</v>
       </c>
     </row>
     <row r="6">
@@ -7384,68 +7377,64 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.2380398983964456</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.1668426208539695</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>0.05142325442912488</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1154607916375272</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0</v>
+        <v>0.9239766081871345</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.05057619817857784</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.3756402276831903</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.1632378494964285</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.3039907952816518</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1517821321501123</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.5657431775791431</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0</v>
+        <v>-0.07611122125507053</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.05143695656071312</v>
+        <v>0.198747981851543</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2535130943000159</v>
+        <v>0.3493382847994992</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1612078395177402</v>
+        <v>-0.1116030758516073</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="n">
-        <v>0.04615004753547058</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.03928937762398355</v>
-      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7490,68 +7479,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.0520480753590512</v>
+        <v>0.07790371755156777</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.04977130173806421</v>
+        <v>0.01591556172396702</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.0653683722520295</v>
+        <v>0.1326921036499702</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2161775406597309</v>
+        <v>0.182346219726028</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2374052086143446</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1284458931702925</v>
+        <v>0.1049397228500237</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5555413873337464</v>
+        <v>0.7662401902298601</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.4134685021818567</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.08056924670644672</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.7694870630425669</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>-0.09083171626673225</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.01791805706482619</v>
+        <v>0.04369407457614072</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.09116441700638167</v>
+        <v>0.08381351492481048</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.09996887029223012</v>
+        <v>-0.03701692200383122</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.04615004753547058</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>0.02142863298018183</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7596,67 +7581,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1434436149079494</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.07768638647757431</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>-0.07611122125507064</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>0.01299867294183905</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.06482391622384889</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>0.2319688109161793</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.465299433644307</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.036483651193696</v>
       </c>
       <c r="T8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1306628532906307</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2645282174188184</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.2431705793713567</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0</v>
+        <v>-0.07611122125507064</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05143695656071312</v>
+        <v>0.1071539192778188</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.2535130943000159</v>
+        <v>0.4372832261827635</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1612078395177402</v>
+        <v>-0.2296898070547482</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.1877889693631971</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>-0.1307501836098439</v>
+        <v>-0.1579827546099043</v>
       </c>
     </row>
     <row r="9">
@@ -7702,67 +7687,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.0520480753590512</v>
+        <v>0.01695327757228604</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.04977130173806421</v>
+        <v>-0.04152973646048097</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0653683722520295</v>
+        <v>0.120962550033912</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2161775406597309</v>
+        <v>0.1697143146176368</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9961013645224172</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2214796402899178</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1284458931702925</v>
+        <v>0.128014615636332</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.5555413873337464</v>
+        <v>0.7148394203240476</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.3062642034833811</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.1503033291826368</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.5699741121993481</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>-0.09083171626673225</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.01791805706482619</v>
+        <v>-0.01532196926280427</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.09116441700638167</v>
+        <v>0.1064472207641982</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.09996887029223012</v>
+        <v>-0.1100542237730052</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.1877889693631971</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.08068656438877009</v>
+        <v>-0.07570585866239699</v>
       </c>
     </row>
   </sheetData>
@@ -7776,7 +7761,1031 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947872</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.03273688296640065</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.0374773260509732</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1977751279185385</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.1023794629725772</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.2772716108878875</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1976947509848085</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.03416668980664972</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.8817737245150478</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1977751279185385</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.2056048719871759</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.06927704843308924</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.6961577284525311</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.04392132259347603</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>0.04942158102667205</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.2535130943000159</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.1628156213137224</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1307501836098439</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>-0.0501331017860881</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.05478828804265878</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.065218646957157</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.2149911464478617</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.1284458931702925</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.5555413873337464</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.08500796058565951</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.1623774629532012</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.2878285332916924</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>-0.04770979298828082</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>-0.01798499137756659</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.09116441700638167</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1000302123885239</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.08068656438877009</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0.04942158102667205</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.2535130943000159</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.1628156213137224</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="n">
+        <v>0.04615004753547058</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.03928937762398355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>-0.0501331017860881</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.05478828804265878</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.065218646957157</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.2149911464478617</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.1284458931702925</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.5555413873337464</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.08500796058565951</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1623774629532012</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.2878285332916924</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.04770979298828082</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>-0.01798499137756659</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.09116441700638167</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.1000302123885239</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.04615004753547058</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0.02142863298018183</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.04942158102667205</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.2535130943000159</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.1628156213137224</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.1307501836098439</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.0501331017860881</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.05478828804265878</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.065218646957157</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.2149911464478617</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.1284458931702925</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.5555413873337464</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.08500796058565951</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1623774629532012</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.2878285332916924</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.04770979298828082</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.01798499137756659</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.09116441700638167</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1000302123885239</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.08068656438877009</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7882,24 +8891,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -7930,20 +8937,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -7977,23 +8984,23 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8023,19 +9030,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -8068,24 +9077,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -8116,21 +9123,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -8147,37 +9156,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -8204,27 +9211,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -8251,25 +9256,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -8296,25 +9303,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -8341,24 +9350,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -8388,27 +9395,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -8425,24 +9430,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8452,10 +9457,10 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -8472,37 +9477,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -8529,25 +9534,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -8574,25 +9581,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -8619,27 +9628,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -8666,32 +9675,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
